--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,10 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>68</v>
@@ -729,6 +733,132 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>60</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>52</v>
+      </c>
+      <c r="B30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>38</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>39</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
         <v>1000</v>
       </c>
     </row>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +862,62 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>196</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>197</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>198</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>200</v>
+      </c>
+      <c r="B39" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,10 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>68</v>
@@ -915,6 +911,174 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>201</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>202</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>204</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>205</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>206</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>207</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>208</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>209</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>210</v>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>211</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>212</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>214</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
         <v>1000</v>
       </c>
     </row>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,104 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>216</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>217</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>218</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>219</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>221</v>
+      </c>
+      <c r="B56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>222</v>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>223</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,6 +1180,216 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120</v>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>228</v>
+      </c>
+      <c r="B60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>76</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>233</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>12</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>230</v>
+      </c>
+      <c r="B65" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>234</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>238</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>232</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>11</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>236</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>119</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,6 +1390,76 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>239</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>240</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>241</v>
+      </c>
+      <c r="B76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>242</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>243</v>
+      </c>
+      <c r="B78" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
